--- a/VerveStacks_UZB_grids_kan15/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_UZB_grids_kan15/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_UZB_grids_kan15\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D86E29A7-5FC5-4691-AD1E-4CAAAEC891C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BA78D24-77B5-4EE4-A125-0F0AA07176EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="23520" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc" sheetId="7" r:id="rId1"/>
@@ -764,18 +764,72 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_UZB_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_UZB_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_UZB_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_UZB_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_UZB_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_UZB_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_UZB_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_UZB_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_UZB_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_UZB_003</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 3</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_UZB_004</t>
   </si>
   <si>
@@ -818,6 +872,42 @@
     <t>connecting solar to buses in cluster 13</t>
   </si>
   <si>
+    <t>distr_solelc_spv_UZB_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_UZB_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_UZB_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_UZB_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_UZB_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_UZB_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_UZB_008</t>
   </si>
   <si>
@@ -836,352 +926,262 @@
     <t>connecting solar to buses in cluster 24</t>
   </si>
   <si>
-    <t>distr_solelc_spv_UZB_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_UZB_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_UZB_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_UZB_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_UZB_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_UZB_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_UZB_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_UZB_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_UZB_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_UZB_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_UZB_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_UZB_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_UZB_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_UZB_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_UZB_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD22</t>
   </si>
   <si>
+    <t>e_Samarkand_UZB</t>
+  </si>
+  <si>
+    <t>e_ZarafshonShahri_UZB</t>
+  </si>
+  <si>
+    <t>e_Navoiy_UZB</t>
+  </si>
+  <si>
+    <t>e_Guzor_UZB</t>
+  </si>
+  <si>
+    <t>e_Druzhba_UZB</t>
+  </si>
+  <si>
+    <t>e_Nukus_UZB</t>
+  </si>
+  <si>
+    <t>e_Namangan_UZB</t>
+  </si>
+  <si>
     <t>e_Andijon_UZB</t>
   </si>
   <si>
-    <t>e_Druzhba_UZB</t>
-  </si>
-  <si>
     <t>e_Tashkent_UZB</t>
   </si>
   <si>
-    <t>e_ZarafshonShahri_UZB</t>
-  </si>
-  <si>
     <t>e_Termiz_UZB</t>
   </si>
   <si>
     <t>e_Bukhara_UZB</t>
   </si>
   <si>
-    <t>e_Nukus_UZB</t>
-  </si>
-  <si>
     <t>e_Bekobod_UZB</t>
   </si>
   <si>
+    <t>e_BeshkentShahri_UZB</t>
+  </si>
+  <si>
     <t>e_Qarshi_UZB</t>
   </si>
   <si>
     <t>e_Denov_UZB</t>
   </si>
   <si>
-    <t>e_BeshkentShahri_UZB</t>
-  </si>
-  <si>
-    <t>e_Namangan_UZB</t>
-  </si>
-  <si>
-    <t>e_Navoiy_UZB</t>
-  </si>
-  <si>
-    <t>e_Samarkand_UZB</t>
-  </si>
-  <si>
-    <t>e_Guzor_UZB</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_UZB_020</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 20</t>
   </si>
   <si>
+    <t>distr_wonelc_won_UZB_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_UZB_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_UZB_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_UZB_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_UZB_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_UZB_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_UZB_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_UZB_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_UZB_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_UZB_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_UZB_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_UZB_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_UZB_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_UZB_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_UZB_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_UZB_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_UZB_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_UZB_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_UZB_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_UZB_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_UZB_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_UZB_011</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 11</t>
   </si>
   <si>
-    <t>distr_wonelc_won_UZB_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_UZB_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_UZB_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_UZB_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_UZB_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_UZB_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_UZB_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_UZB_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_UZB_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_UZB_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_UZB_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_UZB_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_UZB_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_UZB_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_UZB_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_UZB_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_UZB_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_UZB_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_UZB_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_UZB_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_UZB_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
     <t>elc_won_UZB_020</t>
   </si>
   <si>
+    <t>elc_won_UZB_009</t>
+  </si>
+  <si>
+    <t>elc_won_UZB_001</t>
+  </si>
+  <si>
+    <t>elc_won_UZB_013</t>
+  </si>
+  <si>
+    <t>elc_won_UZB_002</t>
+  </si>
+  <si>
+    <t>elc_won_UZB_019</t>
+  </si>
+  <si>
+    <t>elc_won_UZB_012</t>
+  </si>
+  <si>
+    <t>elc_won_UZB_004</t>
+  </si>
+  <si>
+    <t>elc_won_UZB_008</t>
+  </si>
+  <si>
+    <t>elc_won_UZB_018</t>
+  </si>
+  <si>
+    <t>elc_won_UZB_015</t>
+  </si>
+  <si>
+    <t>elc_won_UZB_023</t>
+  </si>
+  <si>
+    <t>elc_won_UZB_007</t>
+  </si>
+  <si>
+    <t>elc_won_UZB_021</t>
+  </si>
+  <si>
+    <t>elc_won_UZB_003</t>
+  </si>
+  <si>
+    <t>elc_won_UZB_016</t>
+  </si>
+  <si>
+    <t>elc_won_UZB_022</t>
+  </si>
+  <si>
+    <t>elc_won_UZB_005</t>
+  </si>
+  <si>
+    <t>elc_won_UZB_017</t>
+  </si>
+  <si>
+    <t>elc_won_UZB_010</t>
+  </si>
+  <si>
+    <t>elc_won_UZB_014</t>
+  </si>
+  <si>
+    <t>elc_won_UZB_006</t>
+  </si>
+  <si>
     <t>elc_won_UZB_011</t>
-  </si>
-  <si>
-    <t>elc_won_UZB_009</t>
-  </si>
-  <si>
-    <t>elc_won_UZB_004</t>
-  </si>
-  <si>
-    <t>elc_won_UZB_008</t>
-  </si>
-  <si>
-    <t>elc_won_UZB_018</t>
-  </si>
-  <si>
-    <t>elc_won_UZB_002</t>
-  </si>
-  <si>
-    <t>elc_won_UZB_019</t>
-  </si>
-  <si>
-    <t>elc_won_UZB_012</t>
-  </si>
-  <si>
-    <t>elc_won_UZB_015</t>
-  </si>
-  <si>
-    <t>elc_won_UZB_023</t>
-  </si>
-  <si>
-    <t>elc_won_UZB_006</t>
-  </si>
-  <si>
-    <t>elc_won_UZB_014</t>
-  </si>
-  <si>
-    <t>elc_won_UZB_001</t>
-  </si>
-  <si>
-    <t>elc_won_UZB_013</t>
-  </si>
-  <si>
-    <t>elc_won_UZB_005</t>
-  </si>
-  <si>
-    <t>elc_won_UZB_017</t>
-  </si>
-  <si>
-    <t>elc_won_UZB_007</t>
-  </si>
-  <si>
-    <t>elc_won_UZB_021</t>
-  </si>
-  <si>
-    <t>elc_won_UZB_010</t>
-  </si>
-  <si>
-    <t>elc_won_UZB_003</t>
-  </si>
-  <si>
-    <t>elc_won_UZB_016</t>
-  </si>
-  <si>
-    <t>elc_won_UZB_022</t>
   </si>
   <si>
     <t>e_won_UZB_001</t>
@@ -2775,28 +2775,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{034C1C47-C7B1-48B4-9602-2B825216B37E}">
   <dimension ref="B11:V29"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="12.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.9296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.3984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.59765625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.9296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.3984375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="32.19921875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="3.3984375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.86328125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="7.1328125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4.73046875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="1.73046875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.53125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.265625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="4.265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="32.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="1.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="11" spans="2:22" ht="17.25" thickBot="1">
+    <row r="11" spans="2:22" ht="18" thickBot="1">
       <c r="B11" s="129" t="s">
         <v>0</v>
       </c>
@@ -2808,7 +2808,7 @@
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
     </row>
-    <row r="12" spans="2:22" ht="15" thickTop="1" thickBot="1">
+    <row r="12" spans="2:22" ht="16.5" thickTop="1" thickBot="1">
       <c r="B12" s="2" t="s">
         <v>6</v>
       </c>
@@ -3443,29 +3443,29 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C12EA90E-43F0-4F26-A089-D51219939B11}">
   <dimension ref="B3:Y14"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="9.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.46484375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.86328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.59765625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.59765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.19921875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="1.73046875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.73046875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.796875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="3.796875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.265625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="7.9296875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4.46484375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.796875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.19921875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="37.9296875" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="4.3984375" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.59765625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="6.73046875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="1.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="3.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="38" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="6.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:25">
@@ -3669,7 +3669,7 @@
       <c r="X7" s="9"/>
       <c r="Y7" s="9"/>
     </row>
-    <row r="8" spans="2:25" ht="17.649999999999999">
+    <row r="8" spans="2:25" ht="18">
       <c r="B8" s="6"/>
       <c r="E8" s="12"/>
       <c r="F8" t="s">
@@ -3785,28 +3785,28 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73A64BB3-8019-4461-A511-24783E2ADCDE}">
   <dimension ref="A1:Z29"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.1328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.1328125" customWidth="1"/>
+    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.140625" customWidth="1"/>
     <col min="3" max="5" width="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="11.86328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.59765625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20.265625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.59765625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.265625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.59765625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.86328125" customWidth="1"/>
-    <col min="16" max="16" width="4.3984375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.1328125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.9296875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="18.1328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.85546875" customWidth="1"/>
+    <col min="16" max="16" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="24" customWidth="1"/>
-    <col min="23" max="23" width="4.53125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="4.19921875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="7.1328125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="4.5703125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="7.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="33.75" customHeight="1">
@@ -3927,7 +3927,7 @@
       <c r="Q3" s="13"/>
       <c r="R3" s="13"/>
     </row>
-    <row r="4" spans="1:18" ht="26.25">
+    <row r="4" spans="1:18" ht="25.5">
       <c r="C4" s="15">
         <v>2020</v>
       </c>
@@ -4805,7 +4805,7 @@
       <c r="Q23" s="109"/>
       <c r="R23" s="109"/>
     </row>
-    <row r="26" spans="1:26" ht="17.25" thickBot="1">
+    <row r="26" spans="1:26" ht="18" thickBot="1">
       <c r="C26" s="129" t="s">
         <v>110</v>
       </c>
@@ -4813,7 +4813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:26" ht="14.65" thickTop="1">
+    <row r="27" spans="1:26" ht="15.75" thickTop="1">
       <c r="A27" s="130" t="s">
         <v>3</v>
       </c>
@@ -5069,9 +5069,9 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C3E71C6-6543-4ECE-AEEB-29E06071836A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BA51D3A-D4E0-4D69-BB7B-21C40DB2B346}">
   <dimension ref="B9:AP36"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="9" spans="2:42">
       <c r="B9" t="s">
@@ -5265,16 +5265,16 @@
         <v>233</v>
       </c>
       <c r="Y11" t="s">
-        <v>207</v>
+        <v>226</v>
       </c>
       <c r="Z11" t="s">
         <v>289</v>
       </c>
       <c r="AA11">
-        <v>0.99740969578877137</v>
+        <v>0.99541056340593537</v>
       </c>
       <c r="AB11">
-        <v>22.232802456527729</v>
+        <v>42.334113814968923</v>
       </c>
       <c r="AD11" t="s">
         <v>232</v>
@@ -5304,7 +5304,7 @@
         <v>350</v>
       </c>
       <c r="AN11" t="s">
-        <v>302</v>
+        <v>289</v>
       </c>
       <c r="AO11">
         <v>0.99533262102489828</v>
@@ -5375,16 +5375,16 @@
         <v>237</v>
       </c>
       <c r="Y12" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="Z12" t="s">
         <v>290</v>
       </c>
       <c r="AA12">
-        <v>0.99421942886742376</v>
+        <v>0.99410292804687739</v>
       </c>
       <c r="AB12">
-        <v>68.507017555362793</v>
+        <v>60.413338593981713</v>
       </c>
       <c r="AD12" t="s">
         <v>232</v>
@@ -5414,13 +5414,13 @@
         <v>351</v>
       </c>
       <c r="AN12" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="AO12">
-        <v>0.98849164675315393</v>
+        <v>0.99645771184810483</v>
       </c>
       <c r="AP12">
-        <v>193.63783372428196</v>
+        <v>32.882484422008979</v>
       </c>
     </row>
     <row r="13" spans="2:42">
@@ -5485,16 +5485,16 @@
         <v>239</v>
       </c>
       <c r="Y13" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="Z13" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AA13">
-        <v>0.99558408503515095</v>
+        <v>0.98707940759302537</v>
       </c>
       <c r="AB13">
-        <v>32.408841762315092</v>
+        <v>209.47770881406512</v>
       </c>
       <c r="AD13" t="s">
         <v>232</v>
@@ -5524,13 +5524,13 @@
         <v>352</v>
       </c>
       <c r="AN13" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="AO13">
-        <v>0.99645771184810483</v>
+        <v>0.99099089541293395</v>
       </c>
       <c r="AP13">
-        <v>32.882484422008979</v>
+        <v>57.597216108722129</v>
       </c>
     </row>
     <row r="14" spans="2:42">
@@ -5595,16 +5595,16 @@
         <v>241</v>
       </c>
       <c r="Y14" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Z14" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AA14">
-        <v>0.99359385075910645</v>
+        <v>0.9874890856882762</v>
       </c>
       <c r="AB14">
-        <v>79.655777902014904</v>
+        <v>167.01041102415843</v>
       </c>
       <c r="AD14" t="s">
         <v>232</v>
@@ -5634,13 +5634,13 @@
         <v>353</v>
       </c>
       <c r="AN14" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="AO14">
-        <v>0.99459971359982058</v>
+        <v>0.9885344001200852</v>
       </c>
       <c r="AP14">
-        <v>55.397912760263836</v>
+        <v>89.909676092483778</v>
       </c>
     </row>
     <row r="15" spans="2:42">
@@ -5705,16 +5705,16 @@
         <v>243</v>
       </c>
       <c r="Y15" t="s">
-        <v>227</v>
+        <v>206</v>
       </c>
       <c r="Z15" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AA15">
-        <v>0.99725396946371203</v>
+        <v>0.99387687085500998</v>
       </c>
       <c r="AB15">
-        <v>39.444454813786322</v>
+        <v>44.868245132242109</v>
       </c>
       <c r="AD15" t="s">
         <v>232</v>
@@ -5744,13 +5744,13 @@
         <v>354</v>
       </c>
       <c r="AN15" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="AO15">
-        <v>0.99661559581486781</v>
+        <v>0.99586307656879591</v>
       </c>
       <c r="AP15">
-        <v>30.379612756542521</v>
+        <v>32.989733772109844</v>
       </c>
     </row>
     <row r="16" spans="2:42">
@@ -5815,16 +5815,16 @@
         <v>245</v>
       </c>
       <c r="Y16" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="Z16" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AA16">
-        <v>0.99442651185824926</v>
+        <v>0.99746948827313053</v>
       </c>
       <c r="AB16">
-        <v>46.840522221104273</v>
+        <v>27.711344775916295</v>
       </c>
       <c r="AD16" t="s">
         <v>232</v>
@@ -5854,13 +5854,13 @@
         <v>355</v>
       </c>
       <c r="AN16" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AO16">
-        <v>0.98959180427949245</v>
+        <v>0.99238765464473333</v>
       </c>
       <c r="AP16">
-        <v>171.20639084469656</v>
+        <v>99.827429558911234</v>
       </c>
     </row>
     <row r="17" spans="2:42">
@@ -5925,16 +5925,16 @@
         <v>247</v>
       </c>
       <c r="Y17" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="Z17" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="AA17">
-        <v>0.98818259224771055</v>
+        <v>0.99462759208841123</v>
       </c>
       <c r="AB17">
-        <v>163.27988843511031</v>
+        <v>55.397912760263836</v>
       </c>
       <c r="AD17" t="s">
         <v>232</v>
@@ -5964,13 +5964,13 @@
         <v>356</v>
       </c>
       <c r="AN17" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="AO17">
-        <v>0.99586307656879591</v>
+        <v>0.98599669066064011</v>
       </c>
       <c r="AP17">
-        <v>32.989733772109844</v>
+        <v>179.1356014534291</v>
       </c>
     </row>
     <row r="18" spans="2:42">
@@ -6035,16 +6035,16 @@
         <v>249</v>
       </c>
       <c r="Y18" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="Z18" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AA18">
-        <v>0.99495486998555394</v>
+        <v>0.98627266925285662</v>
       </c>
       <c r="AB18">
-        <v>55.790178312258959</v>
+        <v>124.40245534922683</v>
       </c>
       <c r="AD18" t="s">
         <v>232</v>
@@ -6074,13 +6074,13 @@
         <v>357</v>
       </c>
       <c r="AN18" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AO18">
-        <v>0.99238765464473333</v>
+        <v>0.99459971359982058</v>
       </c>
       <c r="AP18">
-        <v>99.827429558911234</v>
+        <v>55.397912760263836</v>
       </c>
     </row>
     <row r="19" spans="2:42">
@@ -6145,16 +6145,16 @@
         <v>251</v>
       </c>
       <c r="Y19" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="Z19" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AA19">
-        <v>0.99714948449220475</v>
+        <v>0.99620842217046068</v>
       </c>
       <c r="AB19">
-        <v>19.270241185740602</v>
+        <v>46.073081693183958</v>
       </c>
       <c r="AD19" t="s">
         <v>232</v>
@@ -6184,13 +6184,13 @@
         <v>358</v>
       </c>
       <c r="AN19" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="AO19">
-        <v>0.98599669066064011</v>
+        <v>0.99661559581486781</v>
       </c>
       <c r="AP19">
-        <v>179.1356014534291</v>
+        <v>30.379612756542521</v>
       </c>
     </row>
     <row r="20" spans="2:42">
@@ -6255,16 +6255,16 @@
         <v>253</v>
       </c>
       <c r="Y20" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="Z20" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="AA20">
-        <v>0.99730727100006022</v>
+        <v>0.99740969578877137</v>
       </c>
       <c r="AB20">
-        <v>30.379612756542521</v>
+        <v>22.232802456527729</v>
       </c>
       <c r="AD20" t="s">
         <v>232</v>
@@ -6294,13 +6294,13 @@
         <v>359</v>
       </c>
       <c r="AN20" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="AO20">
-        <v>0.98116028570890745</v>
+        <v>0.98959180427949245</v>
       </c>
       <c r="AP20">
-        <v>236.7122916988269</v>
+        <v>171.20639084469656</v>
       </c>
     </row>
     <row r="21" spans="2:42">
@@ -6365,16 +6365,16 @@
         <v>255</v>
       </c>
       <c r="Y21" t="s">
-        <v>228</v>
+        <v>208</v>
       </c>
       <c r="Z21" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="AA21">
-        <v>0.99686420457588842</v>
+        <v>0.99421942886742376</v>
       </c>
       <c r="AB21">
-        <v>36.221844288496001</v>
+        <v>68.507017555362793</v>
       </c>
       <c r="AD21" t="s">
         <v>232</v>
@@ -6407,10 +6407,10 @@
         <v>294</v>
       </c>
       <c r="AO21">
-        <v>0.99597513010967187</v>
+        <v>0.98116028570890745</v>
       </c>
       <c r="AP21">
-        <v>19.835166435097744</v>
+        <v>236.7122916988269</v>
       </c>
     </row>
     <row r="22" spans="2:42">
@@ -6475,16 +6475,16 @@
         <v>257</v>
       </c>
       <c r="Y22" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="Z22" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="AA22">
-        <v>0.98707940759302537</v>
+        <v>0.99558408503515095</v>
       </c>
       <c r="AB22">
-        <v>209.47770881406512</v>
+        <v>32.408841762315092</v>
       </c>
       <c r="AD22" t="s">
         <v>232</v>
@@ -6514,13 +6514,13 @@
         <v>361</v>
       </c>
       <c r="AN22" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="AO22">
-        <v>0.99107804030291347</v>
+        <v>0.99597513010967187</v>
       </c>
       <c r="AP22">
-        <v>97.57057765989417</v>
+        <v>19.835166435097744</v>
       </c>
     </row>
     <row r="23" spans="2:42">
@@ -6585,16 +6585,16 @@
         <v>259</v>
       </c>
       <c r="Y23" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="Z23" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AA23">
-        <v>0.9874890856882762</v>
+        <v>0.99359385075910645</v>
       </c>
       <c r="AB23">
-        <v>167.01041102415843</v>
+        <v>79.655777902014904</v>
       </c>
       <c r="AD23" t="s">
         <v>232</v>
@@ -6624,13 +6624,13 @@
         <v>362</v>
       </c>
       <c r="AN23" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="AO23">
-        <v>0.98000283232188701</v>
+        <v>0.99813280159000806</v>
       </c>
       <c r="AP23">
-        <v>236.4899183136541</v>
+        <v>4.9862526586665217</v>
       </c>
     </row>
     <row r="24" spans="2:42">
@@ -6695,16 +6695,16 @@
         <v>261</v>
       </c>
       <c r="Y24" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="Z24" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AA24">
-        <v>0.99463308182243737</v>
+        <v>0.99725396946371203</v>
       </c>
       <c r="AB24">
-        <v>45.592831205113754</v>
+        <v>39.444454813786322</v>
       </c>
       <c r="AD24" t="s">
         <v>232</v>
@@ -6734,13 +6734,13 @@
         <v>363</v>
       </c>
       <c r="AN24" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AO24">
-        <v>0.99099089541293395</v>
+        <v>0.99646421008232766</v>
       </c>
       <c r="AP24">
-        <v>57.597216108722129</v>
+        <v>39.444454813786322</v>
       </c>
     </row>
     <row r="25" spans="2:42">
@@ -6805,16 +6805,16 @@
         <v>263</v>
       </c>
       <c r="Y25" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="Z25" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="AA25">
-        <v>0.97981003879732587</v>
+        <v>0.99442651185824926</v>
       </c>
       <c r="AB25">
-        <v>250.06771666808109</v>
+        <v>46.840522221104273</v>
       </c>
       <c r="AD25" t="s">
         <v>232</v>
@@ -6844,13 +6844,13 @@
         <v>364</v>
       </c>
       <c r="AN25" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="AO25">
-        <v>0.9885344001200852</v>
+        <v>0.99420933125715982</v>
       </c>
       <c r="AP25">
-        <v>89.909676092483778</v>
+        <v>68.507017555362793</v>
       </c>
     </row>
     <row r="26" spans="2:42">
@@ -6915,16 +6915,16 @@
         <v>265</v>
       </c>
       <c r="Y26" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="Z26" t="s">
         <v>294</v>
       </c>
       <c r="AA26">
-        <v>0.99651747016421222</v>
+        <v>0.98818259224771055</v>
       </c>
       <c r="AB26">
-        <v>24.589897856155424</v>
+        <v>163.27988843511031</v>
       </c>
       <c r="AD26" t="s">
         <v>232</v>
@@ -6954,13 +6954,13 @@
         <v>365</v>
       </c>
       <c r="AN26" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="AO26">
-        <v>0.9950545353200021</v>
+        <v>0.98789229629876341</v>
       </c>
       <c r="AP26">
-        <v>47.806816980272153</v>
+        <v>167.49834100111656</v>
       </c>
     </row>
     <row r="27" spans="2:42">
@@ -7025,16 +7025,16 @@
         <v>267</v>
       </c>
       <c r="Y27" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Z27" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="AA27">
-        <v>0.99680934868439053</v>
+        <v>0.99495486998555394</v>
       </c>
       <c r="AB27">
-        <v>32.882484422008979</v>
+        <v>55.790178312258959</v>
       </c>
       <c r="AD27" t="s">
         <v>232</v>
@@ -7064,13 +7064,13 @@
         <v>366</v>
       </c>
       <c r="AN27" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="AO27">
-        <v>0.99507839343447024</v>
+        <v>0.99513983210165879</v>
       </c>
       <c r="AP27">
-        <v>39.734195094094147</v>
+        <v>44.249573268028108</v>
       </c>
     </row>
     <row r="28" spans="2:42">
@@ -7135,16 +7135,16 @@
         <v>269</v>
       </c>
       <c r="Y28" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="Z28" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="AA28">
-        <v>0.99620842217046068</v>
+        <v>0.99541032471511048</v>
       </c>
       <c r="AB28">
-        <v>46.073081693183958</v>
+        <v>30.447662679312035</v>
       </c>
       <c r="AD28" t="s">
         <v>232</v>
@@ -7174,13 +7174,13 @@
         <v>367</v>
       </c>
       <c r="AN28" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="AO28">
-        <v>0.99813280159000806</v>
+        <v>0.9950545353200021</v>
       </c>
       <c r="AP28">
-        <v>4.9862526586665217</v>
+        <v>47.806816980272153</v>
       </c>
     </row>
     <row r="29" spans="2:42">
@@ -7245,16 +7245,16 @@
         <v>271</v>
       </c>
       <c r="Y29" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="Z29" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AA29">
-        <v>0.99541032471511048</v>
+        <v>0.99463308182243737</v>
       </c>
       <c r="AB29">
-        <v>30.447662679312035</v>
+        <v>45.592831205113754</v>
       </c>
       <c r="AD29" t="s">
         <v>232</v>
@@ -7284,13 +7284,13 @@
         <v>368</v>
       </c>
       <c r="AN29" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="AO29">
-        <v>0.99646421008232766</v>
+        <v>0.99507839343447024</v>
       </c>
       <c r="AP29">
-        <v>39.444454813786322</v>
+        <v>39.734195094094147</v>
       </c>
     </row>
     <row r="30" spans="2:42">
@@ -7355,16 +7355,16 @@
         <v>273</v>
       </c>
       <c r="Y30" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="Z30" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AA30">
-        <v>0.99410292804687739</v>
+        <v>0.97981003879732587</v>
       </c>
       <c r="AB30">
-        <v>60.413338593981713</v>
+        <v>250.06771666808109</v>
       </c>
       <c r="AD30" t="s">
         <v>232</v>
@@ -7394,7 +7394,7 @@
         <v>369</v>
       </c>
       <c r="AN30" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AO30">
         <v>0.99528538841747116</v>
@@ -7465,16 +7465,16 @@
         <v>275</v>
       </c>
       <c r="Y31" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="Z31" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="AA31">
-        <v>0.99541056340593537</v>
+        <v>0.99651747016421222</v>
       </c>
       <c r="AB31">
-        <v>42.334113814968923</v>
+        <v>24.589897856155424</v>
       </c>
       <c r="AD31" t="s">
         <v>232</v>
@@ -7504,13 +7504,13 @@
         <v>370</v>
       </c>
       <c r="AN31" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="AO31">
-        <v>0.99420933125715982</v>
+        <v>0.98000283232188701</v>
       </c>
       <c r="AP31">
-        <v>68.507017555362793</v>
+        <v>236.4899183136541</v>
       </c>
     </row>
     <row r="32" spans="2:42">
@@ -7575,16 +7575,16 @@
         <v>277</v>
       </c>
       <c r="Y32" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="Z32" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="AA32">
-        <v>0.99462759208841123</v>
+        <v>0.99680934868439053</v>
       </c>
       <c r="AB32">
-        <v>55.397912760263836</v>
+        <v>32.882484422008979</v>
       </c>
       <c r="AD32" t="s">
         <v>232</v>
@@ -7614,13 +7614,13 @@
         <v>371</v>
       </c>
       <c r="AN32" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="AO32">
-        <v>0.98789229629876341</v>
+        <v>0.99107804030291347</v>
       </c>
       <c r="AP32">
-        <v>167.49834100111656</v>
+        <v>97.57057765989417</v>
       </c>
     </row>
     <row r="33" spans="2:42">
@@ -7685,16 +7685,16 @@
         <v>279</v>
       </c>
       <c r="Y33" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="Z33" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AA33">
-        <v>0.98627266925285662</v>
+        <v>0.98988844794701147</v>
       </c>
       <c r="AB33">
-        <v>124.40245534922683</v>
+        <v>168.98719170580645</v>
       </c>
       <c r="AD33" t="s">
         <v>232</v>
@@ -7727,10 +7727,10 @@
         <v>294</v>
       </c>
       <c r="AO33">
-        <v>0.99513983210165879</v>
+        <v>0.98849164675315393</v>
       </c>
       <c r="AP33">
-        <v>44.249573268028108</v>
+        <v>193.63783372428196</v>
       </c>
     </row>
     <row r="34" spans="2:42">
@@ -7795,16 +7795,16 @@
         <v>281</v>
       </c>
       <c r="Y34" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="Z34" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AA34">
-        <v>0.99387687085500998</v>
+        <v>0.99714948449220475</v>
       </c>
       <c r="AB34">
-        <v>44.868245132242109</v>
+        <v>19.270241185740602</v>
       </c>
     </row>
     <row r="35" spans="2:42">
@@ -7869,16 +7869,16 @@
         <v>283</v>
       </c>
       <c r="Y35" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Z35" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AA35">
-        <v>0.99746948827313053</v>
+        <v>0.99730727100006022</v>
       </c>
       <c r="AB35">
-        <v>27.711344775916295</v>
+        <v>30.379612756542521</v>
       </c>
     </row>
     <row r="36" spans="2:42">
@@ -7943,16 +7943,16 @@
         <v>285</v>
       </c>
       <c r="Y36" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="Z36" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="AA36">
-        <v>0.98988844794701147</v>
+        <v>0.99686420457588842</v>
       </c>
       <c r="AB36">
-        <v>168.98719170580645</v>
+        <v>36.221844288496001</v>
       </c>
     </row>
   </sheetData>
@@ -7961,9 +7961,9 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A2DCD21-BD0E-452B-BA2B-107A92AB0A0E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD233A2C-4E7E-47BF-BDFF-4B71BFA514E1}">
   <dimension ref="B9:M33"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="9" spans="2:13">
       <c r="B9" t="s">
@@ -8034,7 +8034,7 @@
         <v>373</v>
       </c>
       <c r="K11" t="s">
-        <v>363</v>
+        <v>352</v>
       </c>
       <c r="L11">
         <v>4.7268083204849543</v>
@@ -8069,7 +8069,7 @@
         <v>375</v>
       </c>
       <c r="K12" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="L12">
         <v>11.440345325444774</v>
@@ -8104,7 +8104,7 @@
         <v>377</v>
       </c>
       <c r="K13" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="L13">
         <v>16.147155115189477</v>
@@ -8139,7 +8139,7 @@
         <v>379</v>
       </c>
       <c r="K14" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="L14">
         <v>34.230544040902842</v>
@@ -8174,7 +8174,7 @@
         <v>381</v>
       </c>
       <c r="K15" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="L15">
         <v>0.16637845637511234</v>
@@ -8209,7 +8209,7 @@
         <v>383</v>
       </c>
       <c r="K16" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="L16">
         <v>0.95674268310369837</v>
@@ -8244,7 +8244,7 @@
         <v>385</v>
       </c>
       <c r="K17" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="L17">
         <v>0.71635206157396158</v>
@@ -8279,7 +8279,7 @@
         <v>387</v>
       </c>
       <c r="K18" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="L18">
         <v>3.8364939532296782</v>
@@ -8314,7 +8314,7 @@
         <v>389</v>
       </c>
       <c r="K19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="L19">
         <v>4.6750393337108811</v>
@@ -8384,7 +8384,7 @@
         <v>393</v>
       </c>
       <c r="K21" t="s">
-        <v>351</v>
+        <v>372</v>
       </c>
       <c r="L21">
         <v>40.600199794755959</v>
@@ -8419,7 +8419,7 @@
         <v>395</v>
       </c>
       <c r="K22" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="L22">
         <v>47.313990231137197</v>
@@ -8454,7 +8454,7 @@
         <v>397</v>
       </c>
       <c r="K23" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="L23">
         <v>36.628915042698111</v>
@@ -8489,7 +8489,7 @@
         <v>399</v>
       </c>
       <c r="K24" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="L24">
         <v>23.798400159780527</v>
@@ -8524,7 +8524,7 @@
         <v>401</v>
       </c>
       <c r="K25" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L25">
         <v>15.163650073738904</v>
@@ -8559,7 +8559,7 @@
         <v>403</v>
       </c>
       <c r="K26" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="L26">
         <v>39.116969059897073</v>
@@ -8594,7 +8594,7 @@
         <v>405</v>
       </c>
       <c r="K27" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L27">
         <v>35.560457304383078</v>
@@ -8629,7 +8629,7 @@
         <v>407</v>
       </c>
       <c r="K28" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="L28">
         <v>18.161490571397067</v>
@@ -8664,7 +8664,7 @@
         <v>409</v>
       </c>
       <c r="K29" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="L29">
         <v>11.686482627817888</v>
@@ -8734,7 +8734,7 @@
         <v>413</v>
       </c>
       <c r="K31" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="L31">
         <v>2.3332937378027507</v>
@@ -8769,7 +8769,7 @@
         <v>415</v>
       </c>
       <c r="K32" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="L32">
         <v>19.78452593009527</v>
@@ -8804,7 +8804,7 @@
         <v>417</v>
       </c>
       <c r="K33" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L33">
         <v>8.4055753674903677</v>
@@ -8819,9 +8819,9 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CD9B069-363A-48AC-81C5-96B70AFE1D41}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E506247-D2D4-4CA5-9E91-F9EE1C482E4D}">
   <dimension ref="B9:Y159"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="9" spans="2:25">
       <c r="B9" t="s">
